--- a/branches/chgl-patch-2/ValueSet-mii-vs-onko-systemische-therapie-protokolle.xlsx
+++ b/branches/chgl-patch-2/ValueSet-mii-vs-onko-systemische-therapie-protokolle.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-19T19:10:10+00:00</t>
+    <t>2026-10-17T20:05:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
